--- a/487-mise-à-jour-des-workflows/ig/StructureDefinition-tddui-discriminator.xlsx
+++ b/487-mise-à-jour-des-workflows/ig/StructureDefinition-tddui-discriminator.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T14:12:11+00:00</t>
+    <t>2026-06-30T14:16:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
